--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/153.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/153.xlsx
@@ -426,13 +426,13 @@
         <v>-13.8296206022905</v>
       </c>
       <c r="E2">
-        <v>-9.717283114898793</v>
+        <v>-7.085560445341165</v>
       </c>
       <c r="F2">
-        <v>-1.897213024224381</v>
+        <v>-1.973584074584618</v>
       </c>
       <c r="G2">
-        <v>-8.701124544262491</v>
+        <v>-8.716895983211579</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.16299456573107</v>
       </c>
       <c r="E3">
-        <v>-9.992935856219695</v>
+        <v>-7.915742942797333</v>
       </c>
       <c r="F3">
-        <v>-1.95436580330076</v>
+        <v>-2.176125015963126</v>
       </c>
       <c r="G3">
-        <v>-8.092583373779201</v>
+        <v>-7.850181918848225</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.39321233812994</v>
       </c>
       <c r="E4">
-        <v>-10.4156553194137</v>
+        <v>-8.555494051282947</v>
       </c>
       <c r="F4">
-        <v>-1.917440116176374</v>
+        <v>-1.745514585702183</v>
       </c>
       <c r="G4">
-        <v>-8.036380242158994</v>
+        <v>-7.639008839989195</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.61918183858776</v>
       </c>
       <c r="E5">
-        <v>-10.97262139456509</v>
+        <v>-8.626115603432567</v>
       </c>
       <c r="F5">
-        <v>-1.831385495996183</v>
+        <v>-1.678810476249789</v>
       </c>
       <c r="G5">
-        <v>-7.597024501460157</v>
+        <v>-7.847758599513479</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.83164514437498</v>
       </c>
       <c r="E6">
-        <v>-11.18637895314916</v>
+        <v>-9.997559428181527</v>
       </c>
       <c r="F6">
-        <v>-1.441926080242018</v>
+        <v>-1.489010448960991</v>
       </c>
       <c r="G6">
-        <v>-7.575363601996706</v>
+        <v>-7.399414727675521</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.06380208576853</v>
       </c>
       <c r="E7">
-        <v>-11.59338461153655</v>
+        <v>-10.26064565413114</v>
       </c>
       <c r="F7">
-        <v>-1.351306427760573</v>
+        <v>-1.314471011873367</v>
       </c>
       <c r="G7">
-        <v>-7.284472586552026</v>
+        <v>-7.454538621449926</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.325325237930034</v>
       </c>
       <c r="E8">
-        <v>-11.68723723534551</v>
+        <v>-11.08815182344878</v>
       </c>
       <c r="F8">
-        <v>-0.9326228867488038</v>
+        <v>-1.222194803004372</v>
       </c>
       <c r="G8">
-        <v>-7.53264432235795</v>
+        <v>-7.69540067270514</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.628243348088706</v>
       </c>
       <c r="E9">
-        <v>-12.73757149668458</v>
+        <v>-11.20999947357316</v>
       </c>
       <c r="F9">
-        <v>-0.7393727561232206</v>
+        <v>-0.7882625495857941</v>
       </c>
       <c r="G9">
-        <v>-7.477629676586342</v>
+        <v>-6.782785894439791</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.985763386609335</v>
       </c>
       <c r="E10">
-        <v>-13.69602302040801</v>
+        <v>-11.51657716389245</v>
       </c>
       <c r="F10">
-        <v>-0.5175501952242367</v>
+        <v>-0.8480712034823649</v>
       </c>
       <c r="G10">
-        <v>-6.57134797193762</v>
+        <v>-5.717866158094732</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.396904278086152</v>
       </c>
       <c r="E11">
-        <v>-14.54974905423005</v>
+        <v>-12.54941793013988</v>
       </c>
       <c r="F11">
-        <v>-0.3721897477756271</v>
+        <v>-0.6947249189551518</v>
       </c>
       <c r="G11">
-        <v>-7.229017638223694</v>
+        <v>-5.678755373093782</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.88197611325508</v>
       </c>
       <c r="E12">
-        <v>-13.92574797834312</v>
+        <v>-14.38462730648837</v>
       </c>
       <c r="F12">
-        <v>-0.1807933449240658</v>
+        <v>-0.8711853913182036</v>
       </c>
       <c r="G12">
-        <v>-6.440319890038805</v>
+        <v>-7.284800330560413</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.435497882883182</v>
       </c>
       <c r="E13">
-        <v>-14.73966872563774</v>
+        <v>-14.07212637216705</v>
       </c>
       <c r="F13">
-        <v>0.1364775877925382</v>
+        <v>-0.2456674821911696</v>
       </c>
       <c r="G13">
-        <v>-6.442686930099383</v>
+        <v>-5.518306472987465</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.075559003552422</v>
       </c>
       <c r="E14">
-        <v>-15.5694889451733</v>
+        <v>-15.23883788702924</v>
       </c>
       <c r="F14">
-        <v>0.3034477024573191</v>
+        <v>0.1513224551909098</v>
       </c>
       <c r="G14">
-        <v>-5.947025430868623</v>
+        <v>-6.352507669609636</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.796530644207993</v>
       </c>
       <c r="E15">
-        <v>-16.94577370863646</v>
+        <v>-15.41732769004156</v>
       </c>
       <c r="F15">
-        <v>0.3798923951426235</v>
+        <v>0.02245947226343287</v>
       </c>
       <c r="G15">
-        <v>-5.59623009389083</v>
+        <v>-5.068439750201443</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.602882328166734</v>
       </c>
       <c r="E16">
-        <v>-17.54045744379773</v>
+        <v>-16.8884160568553</v>
       </c>
       <c r="F16">
-        <v>0.7404586801755111</v>
+        <v>0.3777330121269218</v>
       </c>
       <c r="G16">
-        <v>-5.689504714459796</v>
+        <v>-4.318793197197796</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.487929876758427</v>
       </c>
       <c r="E17">
-        <v>-17.70526672683289</v>
+        <v>-18.01515926012579</v>
       </c>
       <c r="F17">
-        <v>1.420026888490578</v>
+        <v>0.7654479758152302</v>
       </c>
       <c r="G17">
-        <v>-5.733392616673914</v>
+        <v>-5.495364392400316</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.437832536052368</v>
       </c>
       <c r="E18">
-        <v>-18.98345568634189</v>
+        <v>-18.18807451163467</v>
       </c>
       <c r="F18">
-        <v>1.646153170214769</v>
+        <v>1.005110191998682</v>
       </c>
       <c r="G18">
-        <v>-5.99200912365624</v>
+        <v>-4.05336358749565</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.445932083459512</v>
       </c>
       <c r="E19">
-        <v>-20.1123997279801</v>
+        <v>-18.40331288121924</v>
       </c>
       <c r="F19">
-        <v>1.891177814627898</v>
+        <v>1.621531294347432</v>
       </c>
       <c r="G19">
-        <v>-6.190026094542207</v>
+        <v>-4.388745024442597</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.493598988766098</v>
       </c>
       <c r="E20">
-        <v>-19.85949351159973</v>
+        <v>-19.46065722032218</v>
       </c>
       <c r="F20">
-        <v>2.33979418929443</v>
+        <v>2.12431832985157</v>
       </c>
       <c r="G20">
-        <v>-5.305812486458265</v>
+        <v>-4.158436992366579</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.583180111485917</v>
       </c>
       <c r="E21">
-        <v>-20.55727701449364</v>
+        <v>-21.05146032600269</v>
       </c>
       <c r="F21">
-        <v>2.530665593635024</v>
+        <v>2.004141973870278</v>
       </c>
       <c r="G21">
-        <v>-5.441581269569316</v>
+        <v>-3.65936232068483</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.698841963359611</v>
       </c>
       <c r="E22">
-        <v>-21.272449857577</v>
+        <v>-20.04440469075493</v>
       </c>
       <c r="F22">
-        <v>2.530285504215318</v>
+        <v>2.280156575636727</v>
       </c>
       <c r="G22">
-        <v>-5.374949919500405</v>
+        <v>-2.708937801815464</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.846157060826422</v>
       </c>
       <c r="E23">
-        <v>-22.81269707943589</v>
+        <v>-21.36263894591377</v>
       </c>
       <c r="F23">
-        <v>2.804998299719276</v>
+        <v>2.276708847858815</v>
       </c>
       <c r="G23">
-        <v>-4.984974276065338</v>
+        <v>-2.722607044347115</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.015852798328288</v>
       </c>
       <c r="E24">
-        <v>-21.86078467217953</v>
+        <v>-22.09716195843191</v>
       </c>
       <c r="F24">
-        <v>3.249554052418621</v>
+        <v>2.49182203864704</v>
       </c>
       <c r="G24">
-        <v>-4.586785169147339</v>
+        <v>-3.674041279605958</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.209485376279154</v>
       </c>
       <c r="E25">
-        <v>-22.83038529890985</v>
+        <v>-21.67895285534954</v>
       </c>
       <c r="F25">
-        <v>3.36101844215908</v>
+        <v>2.779944072137023</v>
       </c>
       <c r="G25">
-        <v>-5.030265849588107</v>
+        <v>-3.816699307984232</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.420487188530707</v>
       </c>
       <c r="E26">
-        <v>-22.67622698674073</v>
+        <v>-22.67816970209002</v>
       </c>
       <c r="F26">
-        <v>3.082739140933553</v>
+        <v>2.577313651374292</v>
       </c>
       <c r="G26">
-        <v>-4.578435973297297</v>
+        <v>-3.874273005457697</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.638700940152318</v>
       </c>
       <c r="E27">
-        <v>-22.43022216474805</v>
+        <v>-22.06857823049549</v>
       </c>
       <c r="F27">
-        <v>3.323126694426276</v>
+        <v>2.499854595050149</v>
       </c>
       <c r="G27">
-        <v>-5.029861963032316</v>
+        <v>-3.486836550451251</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.856729287050341</v>
       </c>
       <c r="E28">
-        <v>-23.20371269610219</v>
+        <v>-22.14713819758056</v>
       </c>
       <c r="F28">
-        <v>3.149807502746498</v>
+        <v>2.452325996821896</v>
       </c>
       <c r="G28">
-        <v>-3.975257886587626</v>
+        <v>-3.96951409007699</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.056486045661369</v>
       </c>
       <c r="E29">
-        <v>-22.25099422047247</v>
+        <v>-22.33751977333703</v>
       </c>
       <c r="F29">
-        <v>3.109755580145035</v>
+        <v>2.621088866582954</v>
       </c>
       <c r="G29">
-        <v>-5.077358359884239</v>
+        <v>-4.019903903730237</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.233724168413052</v>
       </c>
       <c r="E30">
-        <v>-22.46868249449519</v>
+        <v>-22.65058223843529</v>
       </c>
       <c r="F30">
-        <v>3.042855091159126</v>
+        <v>2.468730022694018</v>
       </c>
       <c r="G30">
-        <v>-4.531373257911017</v>
+        <v>-3.249232076006679</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.369419568687905</v>
       </c>
       <c r="E31">
-        <v>-22.92562816423917</v>
+        <v>-21.87433386641048</v>
       </c>
       <c r="F31">
-        <v>3.093210604446439</v>
+        <v>2.474657833935507</v>
       </c>
       <c r="G31">
-        <v>-4.910834608713359</v>
+        <v>-3.522716243005872</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.463522333019204</v>
       </c>
       <c r="E32">
-        <v>-22.32224975898317</v>
+        <v>-21.24758400680089</v>
       </c>
       <c r="F32">
-        <v>2.906469505133312</v>
+        <v>2.494712301942717</v>
       </c>
       <c r="G32">
-        <v>-4.833692276557263</v>
+        <v>-4.161373446259913</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.505958015982943</v>
       </c>
       <c r="E33">
-        <v>-21.67578292354418</v>
+        <v>-21.0059446337516</v>
       </c>
       <c r="F33">
-        <v>3.046055760814229</v>
+        <v>2.404007129341838</v>
       </c>
       <c r="G33">
-        <v>-5.460136877316931</v>
+        <v>-3.55683803587914</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.501741913484968</v>
       </c>
       <c r="E34">
-        <v>-20.9970325969045</v>
+        <v>-21.69228468282812</v>
       </c>
       <c r="F34">
-        <v>2.53095857922938</v>
+        <v>2.278392327246928</v>
       </c>
       <c r="G34">
-        <v>-4.298963029417562</v>
+        <v>-3.403721994142308</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.453572479863884</v>
       </c>
       <c r="E35">
-        <v>-20.36457686004525</v>
+        <v>-20.11025323130047</v>
       </c>
       <c r="F35">
-        <v>2.373337080583438</v>
+        <v>1.961993224636773</v>
       </c>
       <c r="G35">
-        <v>-4.756367864396505</v>
+        <v>-3.881221840544627</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.365638132778673</v>
       </c>
       <c r="E36">
-        <v>-21.38722855977542</v>
+        <v>-20.58601018207231</v>
       </c>
       <c r="F36">
-        <v>2.422526986316987</v>
+        <v>1.808776012141668</v>
       </c>
       <c r="G36">
-        <v>-4.965359293745156</v>
+        <v>-2.981011676414928</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.248326968031377</v>
       </c>
       <c r="E37">
-        <v>-19.76646959853417</v>
+        <v>-19.58819716227421</v>
       </c>
       <c r="F37">
-        <v>2.505047566746875</v>
+        <v>1.670730702316473</v>
       </c>
       <c r="G37">
-        <v>-4.48711788514204</v>
+        <v>-3.566256537938367</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.105440047398671</v>
       </c>
       <c r="E38">
-        <v>-19.80785532249027</v>
+        <v>-18.97437156748251</v>
       </c>
       <c r="F38">
-        <v>2.215812187998338</v>
+        <v>1.59397322771287</v>
       </c>
       <c r="G38">
-        <v>-4.625392751226319</v>
+        <v>-3.923868288181519</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.957268616821215</v>
       </c>
       <c r="E39">
-        <v>-19.06614109324795</v>
+        <v>-19.09835665733851</v>
       </c>
       <c r="F39">
-        <v>2.256735148853293</v>
+        <v>2.092126339708432</v>
       </c>
       <c r="G39">
-        <v>-4.361810425935086</v>
+        <v>-2.75452070334569</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.806965631972774</v>
       </c>
       <c r="E40">
-        <v>-19.03391194373536</v>
+        <v>-18.48134301684541</v>
       </c>
       <c r="F40">
-        <v>1.960331917131477</v>
+        <v>1.824364429467339</v>
       </c>
       <c r="G40">
-        <v>-4.373698594966609</v>
+        <v>-2.717032085658983</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.674961916086469</v>
       </c>
       <c r="E41">
-        <v>-18.62033546956284</v>
+        <v>-18.9332167957008</v>
       </c>
       <c r="F41">
-        <v>2.275074463354082</v>
+        <v>1.524158719842553</v>
       </c>
       <c r="G41">
-        <v>-4.315485962204065</v>
+        <v>-2.664742018866194</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.56419419503518</v>
       </c>
       <c r="E42">
-        <v>-19.07861251066507</v>
+        <v>-17.44120687897162</v>
       </c>
       <c r="F42">
-        <v>2.121084402372243</v>
+        <v>1.495645678540981</v>
       </c>
       <c r="G42">
-        <v>-4.641038389444915</v>
+        <v>-2.588963631472277</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.487667625276618</v>
       </c>
       <c r="E43">
-        <v>-17.95557812760687</v>
+        <v>-17.67160205105987</v>
       </c>
       <c r="F43">
-        <v>2.083913240830964</v>
+        <v>1.815812417523966</v>
       </c>
       <c r="G43">
-        <v>-3.964462197584062</v>
+        <v>-2.397140691290286</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.447017807103138</v>
       </c>
       <c r="E44">
-        <v>-16.52497884689571</v>
+        <v>-16.31115788967554</v>
       </c>
       <c r="F44">
-        <v>1.970321934046069</v>
+        <v>1.522361213628529</v>
       </c>
       <c r="G44">
-        <v>-3.576724482933542</v>
+        <v>-2.312096086931949</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.440306277555341</v>
       </c>
       <c r="E45">
-        <v>-17.1843156054645</v>
+        <v>-16.1057961219017</v>
       </c>
       <c r="F45">
-        <v>2.068071430558823</v>
+        <v>1.66947482352553</v>
       </c>
       <c r="G45">
-        <v>-3.603427343253303</v>
+        <v>-1.881506670821103</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.465515494412622</v>
       </c>
       <c r="E46">
-        <v>-16.41606451853723</v>
+        <v>-14.76539498647532</v>
       </c>
       <c r="F46">
-        <v>2.262566354033941</v>
+        <v>1.608950334555181</v>
       </c>
       <c r="G46">
-        <v>-4.024088433291875</v>
+        <v>-2.470538796441468</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.509122429342776</v>
       </c>
       <c r="E47">
-        <v>-15.55155618810292</v>
+        <v>-15.27302786578715</v>
       </c>
       <c r="F47">
-        <v>1.883926025241101</v>
+        <v>1.366001928597192</v>
       </c>
       <c r="G47">
-        <v>-4.515913010242621</v>
+        <v>-2.746634983871146</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.569213358665164</v>
       </c>
       <c r="E48">
-        <v>-15.50763904717653</v>
+        <v>-14.92764115322213</v>
       </c>
       <c r="F48">
-        <v>1.599965970896893</v>
+        <v>1.403838246622956</v>
       </c>
       <c r="G48">
-        <v>-3.519812894567931</v>
+        <v>-2.652158635271424</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.625336306100537</v>
       </c>
       <c r="E49">
-        <v>-14.45843237586538</v>
+        <v>-13.87001152025671</v>
       </c>
       <c r="F49">
-        <v>1.484662678017408</v>
+        <v>1.171826913716992</v>
       </c>
       <c r="G49">
-        <v>-3.477686202580705</v>
+        <v>-3.393353365513311</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.675612275683087</v>
       </c>
       <c r="E50">
-        <v>-13.60535391382643</v>
+        <v>-13.45669316910263</v>
       </c>
       <c r="F50">
-        <v>1.736494090455097</v>
+        <v>1.562093227635074</v>
       </c>
       <c r="G50">
-        <v>-3.597557746012176</v>
+        <v>-3.172202302398917</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.703598256179375</v>
       </c>
       <c r="E51">
-        <v>-14.33135886673614</v>
+        <v>-13.34860755148755</v>
       </c>
       <c r="F51">
-        <v>1.414578940141466</v>
+        <v>0.7771737344131439</v>
       </c>
       <c r="G51">
-        <v>-3.380382648090447</v>
+        <v>-2.554669690230966</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.70925610541469</v>
       </c>
       <c r="E52">
-        <v>-14.32514580039762</v>
+        <v>-13.68375991279524</v>
       </c>
       <c r="F52">
-        <v>1.277730911988344</v>
+        <v>1.093729623908927</v>
       </c>
       <c r="G52">
-        <v>-3.785815228648371</v>
+        <v>-2.769984261559625</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.68955668505117</v>
       </c>
       <c r="E53">
-        <v>-13.91118893440846</v>
+        <v>-13.25518060423531</v>
       </c>
       <c r="F53">
-        <v>1.421460142344051</v>
+        <v>1.021870551701777</v>
       </c>
       <c r="G53">
-        <v>-3.284413243452514</v>
+        <v>-2.479483890488579</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.648348578384914</v>
       </c>
       <c r="E54">
-        <v>-12.86008030401408</v>
+        <v>-12.84325702307559</v>
       </c>
       <c r="F54">
-        <v>1.223967263571005</v>
+        <v>0.9325416195414153</v>
       </c>
       <c r="G54">
-        <v>-4.184884940679816</v>
+        <v>-2.530876799440224</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.595573543957292</v>
       </c>
       <c r="E55">
-        <v>-13.00410389135403</v>
+        <v>-11.81916074013697</v>
       </c>
       <c r="F55">
-        <v>1.061825868242399</v>
+        <v>0.7195996895632581</v>
       </c>
       <c r="G55">
-        <v>-3.62442944415444</v>
+        <v>-1.935349383471809</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.535422946684118</v>
       </c>
       <c r="E56">
-        <v>-12.76534009929961</v>
+        <v>-10.6765452354696</v>
       </c>
       <c r="F56">
-        <v>1.270493375954785</v>
+        <v>0.6084045298284236</v>
       </c>
       <c r="G56">
-        <v>-3.856713871917403</v>
+        <v>-2.665768287983368</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.484944563685208</v>
       </c>
       <c r="E57">
-        <v>-12.58627970856232</v>
+        <v>-11.09404789660677</v>
       </c>
       <c r="F57">
-        <v>1.2124885630959</v>
+        <v>1.458651892062231</v>
       </c>
       <c r="G57">
-        <v>-4.229964639288072</v>
+        <v>-2.831805388959975</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.443956945509451</v>
       </c>
       <c r="E58">
-        <v>-12.26665095615293</v>
+        <v>-10.71286812548512</v>
       </c>
       <c r="F58">
-        <v>1.097845675583154</v>
+        <v>1.092459491764745</v>
       </c>
       <c r="G58">
-        <v>-4.162806912478417</v>
+        <v>-3.383709746357414</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.428752137331775</v>
       </c>
       <c r="E59">
-        <v>-12.10839437500687</v>
+        <v>-9.716037784546684</v>
       </c>
       <c r="F59">
-        <v>0.8738178041969207</v>
+        <v>0.8700612537654983</v>
       </c>
       <c r="G59">
-        <v>-3.7377163125083</v>
+        <v>-2.39348915956047</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.436291677262139</v>
       </c>
       <c r="E60">
-        <v>-12.86604430428218</v>
+        <v>-9.574889778201607</v>
       </c>
       <c r="F60">
-        <v>0.9360669489091836</v>
+        <v>0.6164624255261796</v>
       </c>
       <c r="G60">
-        <v>-4.452290946068907</v>
+        <v>-3.089706818105819</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.473600967363509</v>
       </c>
       <c r="E61">
-        <v>-11.88167179533885</v>
+        <v>-9.502714959467356</v>
       </c>
       <c r="F61">
-        <v>0.7205847546426615</v>
+        <v>0.794274590888059</v>
       </c>
       <c r="G61">
-        <v>-4.243680229457273</v>
+        <v>-3.554874882374353</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.534853823194273</v>
       </c>
       <c r="E62">
-        <v>-11.10484830711506</v>
+        <v>-10.17322346341307</v>
       </c>
       <c r="F62">
-        <v>0.7794257642248987</v>
+        <v>0.253802481273081</v>
       </c>
       <c r="G62">
-        <v>-4.36247584558848</v>
+        <v>-3.900936139230987</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.61414614038445</v>
       </c>
       <c r="E63">
-        <v>-11.63936220813642</v>
+        <v>-9.386265250360113</v>
       </c>
       <c r="F63">
-        <v>0.5367743031260552</v>
+        <v>0.1967447245516286</v>
       </c>
       <c r="G63">
-        <v>-4.119303033546855</v>
+        <v>-4.041286717368389</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.704109506702691</v>
       </c>
       <c r="E64">
-        <v>-11.2437909466184</v>
+        <v>-8.379920585531559</v>
       </c>
       <c r="F64">
-        <v>0.54517982227225</v>
+        <v>0.2411819288329441</v>
       </c>
       <c r="G64">
-        <v>-4.198487972300682</v>
+        <v>-2.360224797981873</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.78896122180601</v>
       </c>
       <c r="E65">
-        <v>-10.67867814672721</v>
+        <v>-8.941795526507267</v>
       </c>
       <c r="F65">
-        <v>0.7645991094445546</v>
+        <v>0.2903678753017047</v>
       </c>
       <c r="G65">
-        <v>-3.818996826588486</v>
+        <v>-3.033937367951256</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.862287816159687</v>
       </c>
       <c r="E66">
-        <v>-11.10886506355986</v>
+        <v>-9.636907229736652</v>
       </c>
       <c r="F66">
-        <v>0.6373293346680098</v>
+        <v>0.162086112445194</v>
       </c>
       <c r="G66">
-        <v>-3.760694809096381</v>
+        <v>-3.635155611701679</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.903487610797103</v>
       </c>
       <c r="E67">
-        <v>-11.38039689353378</v>
+        <v>-9.354507062144322</v>
       </c>
       <c r="F67">
-        <v>0.5115007322745148</v>
+        <v>0.3605197125320105</v>
       </c>
       <c r="G67">
-        <v>-4.694086571166197</v>
+        <v>-3.428815929329984</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.907930940968553</v>
       </c>
       <c r="E68">
-        <v>-10.35299935304357</v>
+        <v>-7.682318221597956</v>
       </c>
       <c r="F68">
-        <v>0.3590357800892437</v>
+        <v>-0.1656689534316191</v>
       </c>
       <c r="G68">
-        <v>-3.87071416900298</v>
+        <v>-3.34875369600825</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.858495373116872</v>
       </c>
       <c r="E69">
-        <v>-11.15578911122734</v>
+        <v>-8.749358023551315</v>
       </c>
       <c r="F69">
-        <v>0.2625912572508122</v>
+        <v>0.06602326273238347</v>
       </c>
       <c r="G69">
-        <v>-3.720332637881587</v>
+        <v>-3.311248525593847</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.751807169938333</v>
       </c>
       <c r="E70">
-        <v>-10.44396733890965</v>
+        <v>-9.688011058913212</v>
       </c>
       <c r="F70">
-        <v>0.1245673274554758</v>
+        <v>-0.5428974084008451</v>
       </c>
       <c r="G70">
-        <v>-4.045474557475568</v>
+        <v>-3.27843770875413</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.58070518525749</v>
       </c>
       <c r="E71">
-        <v>-9.648450309982204</v>
+        <v>-8.340572674878912</v>
       </c>
       <c r="F71">
-        <v>0.3285605271584424</v>
+        <v>-0.3624650016018711</v>
       </c>
       <c r="G71">
-        <v>-3.709255552507186</v>
+        <v>-3.354709367433399</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.345689647850404</v>
       </c>
       <c r="E72">
-        <v>-10.88424822430541</v>
+        <v>-9.852507877241838</v>
       </c>
       <c r="F72">
-        <v>0.01754285724895111</v>
+        <v>-0.2136916679054895</v>
       </c>
       <c r="G72">
-        <v>-3.860438235649083</v>
+        <v>-2.991112150855244</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.051981410279849</v>
       </c>
       <c r="E73">
-        <v>-11.14469887838256</v>
+        <v>-9.002404622625928</v>
       </c>
       <c r="F73">
-        <v>-0.2628000127843936</v>
+        <v>-0.1762829504768943</v>
       </c>
       <c r="G73">
-        <v>-3.70269736179389</v>
+        <v>-2.499694771005829</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.704435937980342</v>
       </c>
       <c r="E74">
-        <v>-11.03003338803434</v>
+        <v>-9.057430110293129</v>
       </c>
       <c r="F74">
-        <v>-0.05371123929850051</v>
+        <v>-0.5893142450764599</v>
       </c>
       <c r="G74">
-        <v>-3.404946895991839</v>
+        <v>-2.819708655559479</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.316796687744077</v>
       </c>
       <c r="E75">
-        <v>-11.54728021766445</v>
+        <v>-8.671105992698772</v>
       </c>
       <c r="F75">
-        <v>-0.1804409703578805</v>
+        <v>-0.1715666742607156</v>
       </c>
       <c r="G75">
-        <v>-3.737458089956237</v>
+        <v>-2.913920160516058</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.894465986780644</v>
       </c>
       <c r="E76">
-        <v>-11.79498321741001</v>
+        <v>-9.837636368600648</v>
       </c>
       <c r="F76">
-        <v>-0.09937819122315469</v>
+        <v>-0.6300519123393088</v>
       </c>
       <c r="G76">
-        <v>-3.246014225742508</v>
+        <v>-3.227203705988369</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.454146552136352</v>
       </c>
       <c r="E77">
-        <v>-12.44713328772863</v>
+        <v>-11.08991339983776</v>
       </c>
       <c r="F77">
-        <v>-0.2948827272193659</v>
+        <v>-0.3014202652382999</v>
       </c>
       <c r="G77">
-        <v>-3.257607756221035</v>
+        <v>-2.583094034231149</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.001737698609731</v>
       </c>
       <c r="E78">
-        <v>-12.90723983232996</v>
+        <v>-11.39767302187305</v>
       </c>
       <c r="F78">
-        <v>-0.4065237001693966</v>
+        <v>-0.6560904131480064</v>
       </c>
       <c r="G78">
-        <v>-2.148485615835627</v>
+        <v>-2.290729826021492</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.552270260424954</v>
       </c>
       <c r="E79">
-        <v>-13.91960283911471</v>
+        <v>-11.88537608707712</v>
       </c>
       <c r="F79">
-        <v>-0.3376451624951041</v>
+        <v>-0.6669958120817225</v>
       </c>
       <c r="G79">
-        <v>-2.520703492998044</v>
+        <v>-2.330118696847741</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.113971318552543</v>
       </c>
       <c r="E80">
-        <v>-13.17985849606572</v>
+        <v>-12.56797108814931</v>
       </c>
       <c r="F80">
-        <v>-0.4865839934596493</v>
+        <v>-0.5620990507725907</v>
       </c>
       <c r="G80">
-        <v>-2.602914270374765</v>
+        <v>-1.953156807927549</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.6977269612452</v>
       </c>
       <c r="E81">
-        <v>-14.41922937638098</v>
+        <v>-13.03432239840721</v>
       </c>
       <c r="F81">
-        <v>-0.1412885927163865</v>
+        <v>-0.8029165804213554</v>
       </c>
       <c r="G81">
-        <v>-2.457875959753756</v>
+        <v>-1.479735553629612</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.314330047243712</v>
       </c>
       <c r="E82">
-        <v>-16.14585953144756</v>
+        <v>-12.9174741835873</v>
       </c>
       <c r="F82">
-        <v>-0.5028233139165653</v>
+        <v>-0.6447106942926163</v>
       </c>
       <c r="G82">
-        <v>-1.90672971728481</v>
+        <v>-0.8779412749553563</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.970633785250625</v>
       </c>
       <c r="E83">
-        <v>-16.7989696382558</v>
+        <v>-15.26614005682148</v>
       </c>
       <c r="F83">
-        <v>-0.4375413723762359</v>
+        <v>-0.9589892146819975</v>
       </c>
       <c r="G83">
-        <v>-1.464308411416608</v>
+        <v>-1.366177220541532</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.678870052396179</v>
       </c>
       <c r="E84">
-        <v>-17.84114358943304</v>
+        <v>-15.96124723157686</v>
       </c>
       <c r="F84">
-        <v>-0.4394212312978625</v>
+        <v>-0.7921370861079168</v>
       </c>
       <c r="G84">
-        <v>-1.279940819789057</v>
+        <v>-1.479454157258774</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.441893762047827</v>
       </c>
       <c r="E85">
-        <v>-17.72376554315422</v>
+        <v>-16.84771866094837</v>
       </c>
       <c r="F85">
-        <v>-0.5646543602671522</v>
+        <v>-0.2439824190971421</v>
       </c>
       <c r="G85">
-        <v>-0.9575201686283572</v>
+        <v>-1.352772821653023</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.271999921526247</v>
       </c>
       <c r="E86">
-        <v>-19.89841574569566</v>
+        <v>-18.10447435297907</v>
       </c>
       <c r="F86">
-        <v>-0.52164328316269</v>
+        <v>-1.066836420111593</v>
       </c>
       <c r="G86">
-        <v>-1.256171102817089</v>
+        <v>-0.9694778591162047</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.16916600664116</v>
       </c>
       <c r="E87">
-        <v>-22.48811870493611</v>
+        <v>-20.22306657577955</v>
       </c>
       <c r="F87">
-        <v>-0.9819569097206581</v>
+        <v>-0.9607328748948962</v>
       </c>
       <c r="G87">
-        <v>-0.6552011499821123</v>
+        <v>-0.375801038104242</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.140684865742666</v>
       </c>
       <c r="E88">
-        <v>-22.90347034091964</v>
+        <v>-21.30075282012494</v>
       </c>
       <c r="F88">
-        <v>-0.7060333710443472</v>
+        <v>-1.194300198862779</v>
       </c>
       <c r="G88">
-        <v>-1.474329432763982</v>
+        <v>-0.3270300812196988</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.184311736318521</v>
       </c>
       <c r="E89">
-        <v>-23.5434252307356</v>
+        <v>-22.15337390628912</v>
       </c>
       <c r="F89">
-        <v>-0.7865901561390901</v>
+        <v>-1.384051923121157</v>
       </c>
       <c r="G89">
-        <v>-0.2692345771951025</v>
+        <v>-0.9560469758633815</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.299009709358374</v>
       </c>
       <c r="E90">
-        <v>-25.29570919105563</v>
+        <v>-23.74507364982315</v>
       </c>
       <c r="F90">
-        <v>-0.6508554732445213</v>
+        <v>-0.955261170957053</v>
       </c>
       <c r="G90">
-        <v>-0.9615126865487182</v>
+        <v>-0.566435492437634</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.480282609754461</v>
       </c>
       <c r="E91">
-        <v>-27.65085078212078</v>
+        <v>-25.3754510898567</v>
       </c>
       <c r="F91">
-        <v>-0.892947094302257</v>
+        <v>-1.143725342306178</v>
       </c>
       <c r="G91">
-        <v>-0.5879474173518182</v>
+        <v>0.1400448572794551</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.718797852925808</v>
       </c>
       <c r="E92">
-        <v>-29.30741185886668</v>
+        <v>-29.01505810540548</v>
       </c>
       <c r="F92">
-        <v>-1.182305210259241</v>
+        <v>-1.207775160644296</v>
       </c>
       <c r="G92">
-        <v>-1.209780428175282</v>
+        <v>-1.169199760954896</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.008920198259065</v>
       </c>
       <c r="E93">
-        <v>-31.38716788857738</v>
+        <v>-28.90378444208901</v>
       </c>
       <c r="F93">
-        <v>-0.9654317303460052</v>
+        <v>-1.401551873486762</v>
       </c>
       <c r="G93">
-        <v>-0.9316912923309634</v>
+        <v>-0.920137488398907</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.336326803150992</v>
       </c>
       <c r="E94">
-        <v>-33.38220296231558</v>
+        <v>-32.65587195927732</v>
       </c>
       <c r="F94">
-        <v>-1.10948482856142</v>
+        <v>-1.6318013335618</v>
       </c>
       <c r="G94">
-        <v>-1.020198727323379</v>
+        <v>0.2938693557616908</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.694864951769798</v>
       </c>
       <c r="E95">
-        <v>-35.89335274718199</v>
+        <v>-34.47091604086965</v>
       </c>
       <c r="F95">
-        <v>-1.055213602398183</v>
+        <v>-1.439316132893374</v>
       </c>
       <c r="G95">
-        <v>-1.89859901744036</v>
+        <v>-0.139620098241557</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.07203086934574</v>
       </c>
       <c r="E96">
-        <v>-37.76054447120964</v>
+        <v>-37.30001225005159</v>
       </c>
       <c r="F96">
-        <v>-0.9156004237167029</v>
+        <v>-1.098965853871071</v>
       </c>
       <c r="G96">
-        <v>-1.732333488821543</v>
+        <v>-0.3931251229112481</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.456890215923409</v>
       </c>
       <c r="E97">
-        <v>-40.7928627441968</v>
+        <v>-39.6604385702837</v>
       </c>
       <c r="F97">
-        <v>-1.272842510033083</v>
+        <v>-1.21615296493697</v>
       </c>
       <c r="G97">
-        <v>-2.372463884840559</v>
+        <v>-1.374662148758684</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.844017598699791</v>
       </c>
       <c r="E98">
-        <v>-43.07154105164244</v>
+        <v>-40.93049665471193</v>
       </c>
       <c r="F98">
-        <v>-1.204447002663</v>
+        <v>-1.177714046810382</v>
       </c>
       <c r="G98">
-        <v>-1.995793323927822</v>
+        <v>-1.153613712556007</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.213658368681368</v>
       </c>
       <c r="E99">
-        <v>-44.82075697082227</v>
+        <v>-44.62002556772128</v>
       </c>
       <c r="F99">
-        <v>-1.148965825180367</v>
+        <v>-1.487060906979085</v>
       </c>
       <c r="G99">
-        <v>-2.538633407638737</v>
+        <v>-1.936186951493245</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.573717984516803</v>
       </c>
       <c r="E100">
-        <v>-47.50027089081986</v>
+        <v>-46.01255170321294</v>
       </c>
       <c r="F100">
-        <v>-1.525085686008786</v>
+        <v>-1.545819563853719</v>
       </c>
       <c r="G100">
-        <v>-2.816262377653097</v>
+        <v>-2.08060950064395</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.88435160839281</v>
       </c>
       <c r="E101">
-        <v>-49.67561508200296</v>
+        <v>-48.40567360578043</v>
       </c>
       <c r="F101">
-        <v>-1.489165652140704</v>
+        <v>-1.307916844942321</v>
       </c>
       <c r="G101">
-        <v>-3.657448825363131</v>
+        <v>-1.761290830653548</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.185906286121073</v>
       </c>
       <c r="E102">
-        <v>-51.30000814363537</v>
+        <v>-49.70439693067721</v>
       </c>
       <c r="F102">
-        <v>-1.579879535124117</v>
+        <v>-1.783049207751056</v>
       </c>
       <c r="G102">
-        <v>-3.760754398916088</v>
+        <v>-1.404811286984827</v>
       </c>
     </row>
   </sheetData>
